--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0076.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0076.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Khoảnh Khắc "Ta-da".</t>
+          <t>Một khoảnh khắc "ta-da" đầy ấn tượng.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>"Thử Bơi Trong Thủy Triều Tối"</t>
+          <t>"Thử Bơi Trong Bóng Tối"</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dragon Supreme</t>
+          <t>Rồng Tối Thượng</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Fading Maroon</t>
+          <t>Đỏ Thẫm Phai Mờ</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Thử Thách Của Người Xưa</t>
+          <t>Thử Thách Cổ Nhân</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Ace Abjudicator</t>
+          <t>Thẩm Phán Tinh Anh</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Planescape</t>
+          <t>Cảnh Giới</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Ngày Đánh Bại Thần Tính</t>
+          <t>Ngày Lật Đổ Thần Tính</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>World Sunderer</t>
+          <t>Kẻ Phân Rã Thế Giới</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Knockin' Down "Paradise's" Door</t>
+          <t>Đập Cửa "Thiên Đường"</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Green Soliseed</t>
+          <t>Hạt Soliseed Xanh</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Ready Biker One</t>
+          <t>Xe Một sẵn sàng</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Shot Put Enthusiast</t>
+          <t>Tín Đồ Ném Tạ</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Ta Chính Là Phát Bắn</t>
+          <t>Ta chính là phát súng đó.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Trở Thành Ánh Sáng</t>
+          <t>Trở thành Ánh Sáng</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Watch Where Bạn Go</t>
+          <t>Để mắt tới xung quanh đi</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Motorbike Mountaineer</t>
+          <t>Tay Đua Xe Máy Vùng Núi</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Logical Clarity</t>
+          <t>Tính Logic</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Violence Works</t>
+          <t>Bạo Lực Hữu Hiệu</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3D Architect</t>
+          <t>Kiến Trúc Sư 3D</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Stunt Vehicle Pro</t>
+          <t>Xe Đua Chuyên Nghiệp</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Có Cái Gì Vừa Bay Qua Đấy Nhỉ?</t>
+          <t>Vừa có cái gì bay qua à?</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Play-guin Time</t>
+          <t>Giờ Chơi Chim Cánh Cụt</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>I See Bạn</t>
+          <t>Ta Thấy Ngươi</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Cảnh Giới Tồn Tại</t>
+          <t>Cảnh Giới Hiện Hữu</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Highway Star</t>
+          <t>Ngôi Sao Cao Tốc</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Extreme Cornering</t>
+          <t>Cua Gấp Cực Hạn</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Feeling Alive Again</t>
+          <t>Cảm giác sống lại</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Traffic Controller</t>
+          <t>Điều phối viên giao thông</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>When Bạn Believe</t>
+          <t>Khi Ta Tin Tưởng</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Liệu Giờ Đây Có Thể Là—</t>
+          <t>Liệu Thời Gian Có Thể—</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Chuluuluu!</t>
+          <t>Chu-luu-luu!</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Laser Surgery</t>
+          <t>Phẫu Thuật Laser</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Khởi Đầu Chậm Rãi</t>
+          <t>Khởi Đầu Chậm</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Robbie's Dream</t>
+          <t>Giấc Mơ Của Robbie</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Trên Tuyến Đầu</t>
+          <t>Trên Chiến Tuyến</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Đội Soliskin, Tấn Công!</t>
+          <t>Đội Soliskin, tấn công!</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Ngươi Là Mẹ Của Ta Sao?</t>
+          <t>Mẹ có phải là mẹ của con không?</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Bjartr Woods Forever</t>
+          <t>Bjartr Woods Mãi Mãi</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>One Step Away</t>
+          <t>Chỉ Cách Một Bước Chân</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Howling Horizon</t>
+          <t>Chân Trời Gào Thét</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Urban Legends Never Die</t>
+          <t>Huyền Thoại Đô Thị Không Bao Giờ Chết</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>TARD-E Tiến Hóa Siêu Cấp!</t>
+          <t>TIẾN HÓA MEGA TARD-E!</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Chạm tới bầu trời</t>
+          <t>Chạm vào Bầu Trời</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Âm thanh của ngày hôm qua</t>
+          <t>Âm Thanh Ngày Hôm Qua</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Nơi gần gió nhất</t>
+          <t>Nơi Gần Gió Nhất</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Paper Soliskin: Sweet Misha</t>
+          <t>Giấy Da Soliskin: Misha Ngọt Ngào</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Cảnh quan của sự tồn tại</t>
+          <t>Cảnh Giới Hiện Hữu</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Cảnh quan của sự tồn tại</t>
+          <t>Cảnh Giới Hiện Hữu</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Ngai vàng không tạo nên vua</t>
+          <t>Ngai Vàng Không Tạo Nên Vua</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Sights Cô ấy Has Seen</t>
+          <t>Những Điều Nàng Đã Chứng Kiến</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Absolute Glommoth</t>
+          <t>Glommoth Tuyệt Đối</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Ba hang ổ của Soliskin</t>
+          <t>Ba Hầm Trú Ẩn của Soliskin</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Khởi hành, xe máy!</t>
+          <t>Xuất phát nào, xe máy!</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Bay lên đỉnh cao</t>
+          <t>Đưa ta lên đỉnh cao</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Mở khóa tất cả trường lực Voidmatter</t>
+          <t>Mở khóa tất cả Trường Lực Hư Không.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>A Beam Toward Reality</t>
+          <t>Tia Sáng Hướng Về Thực Tại</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Where's My Home</t>
+          <t>Nhà của ta đâu...</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Skilled Craftsman</t>
+          <t>Thợ thủ công lão luyện</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Fishing Master I</t>
+          <t>Bậc Thầy Câu Cá I</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Fishing Master II</t>
+          <t>Bậc Thầy Câu Cá II</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Hunting Master I</t>
+          <t>Bậc Thầy Săn Bắt I</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Hunting Master II</t>
+          <t>Bậc Thầy Săn Bắt II</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Wild Hunter I</t>
+          <t>Thợ Săn Hoang Dã I</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Wild Hunter II</t>
+          <t>Thợ Săn Hoang Dã II</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Thợ đào vàng I</t>
+          <t>Thợ Mỏ Vàng I</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Thợ đào vàng II</t>
+          <t>Thợ Mỏ Vàng II</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Winner Winner Chicken Dinner</t>
+          <t>Thắng Lớn Ăn Thịt Gà</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Fishing Master III</t>
+          <t>Bậc Thầy Câu Cá III</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Hunting Master III</t>
+          <t>Bậc Thầy Săn Bắt III</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Wild Hunter III</t>
+          <t>Thợ Săn Hoang Dã III</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Thợ đào vàng III</t>
+          <t>Thợ Mỏ Vàng III</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Đi theo bản đồ</t>
+          <t>Đi theo Bản Đồ</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Effective Potion I</t>
+          <t>Thuốc Hiệu Quả Cấp I</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Effective Potion II</t>
+          <t>Dược Thần Hiệu II</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Effective Potion III</t>
+          <t>Dược Thần Hiệu III</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Savoring Joy I</t>
+          <t>Niềm Vui Thưởng Thức I</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Savoring Joy II</t>
+          <t>Niềm Vui Thưởng Thức II</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Savoring Joy III</t>
+          <t>Niềm Vui Thưởng Thức III</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Creative Workshop I</t>
+          <t>Xưởng Sáng Tạo I</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Creative Workshop II</t>
+          <t>Xưởng Sáng Tạo II</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Creative Workshop III</t>
+          <t>Xưởng Sáng Tạo III</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Mochelin 1-Star Chef</t>
+          <t>Đầu Bếp Sao Michelin 1 Sao</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Mochelin 2-Star Chef</t>
+          <t>Đầu Bếp Sao Michelin 2 Sao</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Mochelin 3-Star Chef</t>
+          <t>Đầu Bếp Sao Michelin 3 Sao</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Pharmacist's Spell I</t>
+          <t>Phép Thuật Dược Sư I</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Pharmacist's Spell II</t>
+          <t>Phép Thuật Dược Sư II</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Pharmacist's Spell III</t>
+          <t>Phép Thuật Dược Sư III</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Uống thuốc đi!</t>
+          <t>Uống Thuốc Đi!</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Giữ máy quay tiếp tục quay!</t>
+          <t>Tiếp tục quay nào!</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Good Food Always Glow</t>
+          <t>Món Ngon Luôn Rực Rỡ</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Cooking With Heart</t>
+          <t>Nấu Ăn Bằng Cả Tâm Hồn</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Ultimate Gourmet</t>
+          <t>Thưởng Thức Tối Thượng</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Mackerel Gear</t>
+          <t>Bánh răng Mackerel</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Master Angler</t>
+          <t>Sư phụ Câu Cá</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Fish, Big Fish</t>
+          <t>Cá, Cá To</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Fish, Small Fish</t>
+          <t>Cá, Cá Nhỏ</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Feeling Tenta-cular</t>
+          <t>Cảm giác... như bị cuốn vào</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Tất cả Out</t>
+          <t>Tổng Lực</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Câu cá vì tình yêu</t>
+          <t>Câu Cá Tình Yêu</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Nhà sưu tập game cổ điển</t>
+          <t>Nhà Sưu Tầm Game Cổ Điển</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Echoes of the Past: Jinzhou</t>
+          <t>Tiếng Vọng Quá Khứ: Jinzhou</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Echoes of the Past: Jinzhou</t>
+          <t>Tiếng Vọng Quá Khứ: Jinzhou</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Echoes of the Past: Jinzhou</t>
+          <t>Tiếng Vọng Quá Khứ: Jinzhou</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Mở hộp thiết bị đầu cuối</t>
+          <t>Mở Thiết Bị Đầu Cuối</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>World Travel: Jinzhou</t>
+          <t>Du Hành Thế Giới: Jinzhou</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>"Trace On"</t>
+          <t>"Dấu Vết Đã Bật"</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Only Reverberation Remains</t>
+          <t>Chỉ còn Tàn Dư Cộng Hưởng</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Những sinh vật dễ thương và nơi tìm thấy chúng</t>
+          <t>Những Sinh Vật Dễ Thương Và Nơi Tìm Thấy Chúng</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Cremation Tuning I</t>
+          <t>Điều Chỉnh Hỏa Táng I</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Cremation Tuning II</t>
+          <t>Điều Chỉnh Hỏa Táng II</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Cremation Tuning III</t>
+          <t>Điều Chỉnh Hỏa Táng III</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Âm Thanh Trở Về</t>
+          <t>Âm thanh của Sự Trở Về</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Pioneer's Proof: Jinzhou</t>
+          <t>Bằng Chứng Tiên Phong: Jinzhou</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Chest Collector I</t>
+          <t>Người Sưu Tập Rương I</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Chest Collector II</t>
+          <t>Người Sưu Tập Rương II</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Chest Collector III</t>
+          <t>Người Sưu Tầm Rương III</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Thinning Hair, Greater Power</t>
+          <t>Tóc thưa, sức mạnh lớn</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Solaris Landscapes: Ragunna I</t>
+          <t>Cảnh quan Solaris: Ragunna I</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Solaris Landscapes: Ragunna II</t>
+          <t>Cảnh quan Solaris: Ragunna II</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Solaris Landscapes: Ragunna III</t>
+          <t>Cảnh quan Solaris: Ragunna III</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Ride Your Wave</t>
+          <t>Cưỡi Trên Sóng Cảm Xúc</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Mảnh Ghép Nốt Nhấn Lẻ</t>
+          <t>Bản vá của những nốt rời rạc</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Ragunnesi Grandeur</t>
+          <t>Vĩ Đại Ragunnesi</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Từ Thế Giới Mới</t>
+          <t>Từ Tân Thế Giới</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Candy Spells Riddle</t>
+          <t>Câu đố Phép Thuật Kẹo</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Thị Trưởng Phán Qua: Thông Điệp Vô Ngôn</t>
+          <t>Lời Phán Xét Của Quan Toà: Thông Điệp Vô Ngôn</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Researchers' Trusted Confidant</t>
+          <t>Người bạn tâm giao của các nhà nghiên cứu</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Thị Trưởng Phán Qua: Tiếng Gọi Tiền Tuyến</t>
+          <t>Lời Phán Xét Của Quan Toà: Tiếng Gọi Chiến Tuyến</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Shepherd Game</t>
+          <t>Trò Chơi Người Chăn Cừu</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>"Chôn Vùi Dưới Gốc Đào Hoa..."</t>
+          <t>"Chôn vùi dưới gốc cây hoa đào..."</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>A Whispering Melody</t>
+          <t>Giai Điệu Thì Thầm</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Nếu Giai Điệu Là Chân Thật</t>
+          <t>Nếu Giai Điệu Chân Thật</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>The Tuning Master</t>
+          <t>Bậc Thầy Điều Tần</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kitten First</t>
+          <t>Mèo Con Đầu Tiên</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Trở Lại Sự Tĩnh Lặng</t>
+          <t>Quay lại Silence</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Windbrone Tunes</t>
+          <t>Giai Điệu Gió Bay</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>An Ủi Là Vô Nghĩa</t>
+          <t>An ủi cũng vô ích thôi.</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Captivating Bạn Always</t>
+          <t>Mãi Say Lòng Anh</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Người Giữ Trong Bóng Tối</t>
+          <t>Người Gác Bóng Tối</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Tham Gia Là Chìa Khóa</t>
+          <t>Tham gia là Chìa Khóa</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>The Same Sunset</t>
+          <t>Ánh Hoàng Hôn Giống Nhau</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Spring Awakening</t>
+          <t>Xuân Thức Tỉnh</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Núi Non Sau Rừng Rậm</t>
+          <t>Núi Vọng Lâm</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Truyện Cổ Tích Về Mặt Trăng Và Điều Ước</t>
+          <t>Truyện Cổ Tích Về Mặt Trăng Và Những Điều Ước</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>We're Listening</t>
+          <t>Chúng ta đang lắng nghe.</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Vật Chứng Lời Hứa</t>
+          <t>Mãnh Hứa Ước</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>The Moon Knows My Heart</t>
+          <t>Trăng Biết Lòng Ta</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Belated Wish</t>
+          <t>Lời Chúc Muộn Màng</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Paint Me As Your Friend</t>
+          <t>Hãy Vẽ Ta Là Bạn Của Ngươi</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Giữ Gìn Màu Sắc Chân Thật</t>
+          <t>Giữ Lấy Bản Sắc Thật</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>One Last Ocean</t>
+          <t>Đại Dương Cuối Cùng</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Bươm Bướm Vượt Biển</t>
+          <t>Bướm Bay Qua Biển</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Xuyên Qua Cánh Cổng Sao</t>
+          <t>Xuyên qua Cánh Cổng Sao</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Hehe Haha</t>
+          <t>Hehe haha</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Thời Gian Nạp Năng Lúc 3 Giờ Chiều</t>
+          <t>Nạp năng lượng lúc 3 giờ chiều.</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Pale Blue Dot</t>
+          <t>Chấm Xanh Nhạt</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>"Hey, KU-Roro"</t>
+          <t>"Này, KU-Roro"</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Every Loss, Every Gain</t>
+          <t>Mỗi Mất Mát, Mỗi Thành Quả</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Ta Tặng Ngươi Ký Ức Về Một Bông Sơn Trà</t>
+          <t>Ta Dâng Tặng Ngươi Ký Ức Của Một Bông Sứ</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Yet Another Sunrise</t>
+          <t>Một Bình Minh Nữa</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>"Collage Art"</t>
+          <t>"Nghệ thuật cắt dán"</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Câu Trả Lời Trôi Dạt Trên Biển</t>
+          <t>Câu Trả Lời Trôi Dạt Trên Biển Cả</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>The Greatest Show</t>
+          <t>Màn Biểu Diễn Vĩ Đại Nhất</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Total Recollection</t>
+          <t>Tổng Hồi Tưởng</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>A Rover Prepares</t>
+          <t>Vận Mệnh Giả Chuẩn Bị</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Mỗi Ngày Ta Chưa Khiêu Vũ</t>
+          <t>Mỗi Ngày Ta Không Nhảy Múa</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Papers, Please</t>
+          <t>Giấy tờ à, làm ơn!</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Cảnh Đẹp Tuyệt Vời Phía Trước, Hãy Ngắm Nhìn!</t>
+          <t>Cảnh đẹp phía trước, hãy chiêm ngưỡng!</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Cứu Cá Khỏi Chết Chìm</t>
+          <t>Cứu Cá Khỏi Chết Đuối</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Elijah's Prophecy</t>
+          <t>Lời Tiên Tri của Elijah</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Cùng Đi Bắt Sứa Nào...?</t>
+          <t>Đi bắt sứa không cậu...?</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Tormented Prophet</t>
+          <t>Nhà Tiên Tri Đau Khổ</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Nguyên Tố Của Câu Cá</t>
+          <t>Nguyên Tố Câu Cá</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Lãnh Chúa Ánh Sáng</t>
+          <t>Người Gìn Giữ Ánh Sáng</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Cái Chết &amp; Sự Tái Sinh</t>
+          <t>Sinh Tử Luân Hồi</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Học Viện Trên Bầu Trời</t>
+          <t>Chủng Tự Trên Không</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Thử Thách Kiếm Thuật</t>
+          <t>Thử Thách Kiếm Khí</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Requiem Cantor</t>
+          <t>Ca Thương Khúc</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Bubble Bath Time</t>
+          <t>Giờ Tắm Bong Bóng</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Bubble Bath Era</t>
+          <t>Thời Đại Tắm Bong Bóng</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Justice Is Done</t>
+          <t>Công Lý Đã Được Thực Thi</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Smart Camera</t>
+          <t>Máy Ảnh Thông Minh</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Octopus Never Sleeps</t>
+          <t>Bạch tuộc không bao giờ ngủ</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Atheist</t>
+          <t>Kẻ vô thần</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Thanh Kiếm Sắt Của Chiến Thắng Đã Định</t>
+          <t>Thanh Kiếm Sắt Lời Thề Chiến Thắng</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Dana's Mime</t>
+          <t>Diễn xuất của Dana</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Sailor's Legacy</t>
+          <t>Di Sản Của Thủy Thủ</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Moby Dick</t>
+          <t>Cá Voi Trắng</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Special Grade Spirit</t>
+          <t>Tinh Thần Cấp Đặc Biệt</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Cultural Differences</t>
+          <t>Khác Biệt Văn Hóa</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Shine On Bạn Crazy Opal</t>
+          <t>Hãy Tỏa Sáng, Viên Ngọc Điên Cuồng</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>If Our Language Is Cocktail</t>
+          <t>Nếu Ngôn Ngữ Ta Là Cocktail</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Ôi Thuyền Trưởng! Thuyền Trưởng Của Tôi!</t>
+          <t>Ôi Đội trưởng! Đội trưởng của ta!</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>To Dream's Shores</t>
+          <t>Tới Bờ Mộng Ảo</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>From Dream's Shores</t>
+          <t>Từ Bến Bờ Giấc Mơ</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Little Peaceful Life Bạn Created</t>
+          <t>Cuộc Sống Bình Yên Nhỏ Bé Mà Con Đã Tạo Ra</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>The Dark Knight</t>
+          <t>Hắc Kỵ Sĩ</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Good Night, Ragunna</t>
+          <t>Chúc Ngủ Ngon, Ragunna</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Phước Lành Của Ánh Sáng</t>
+          <t>Phúc Lành Ánh Sáng</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Thông Minh Chứ?</t>
+          <t>Thạo việc à?</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Tôi Không Có Y Kasaya</t>
+          <t>Ta không có Kasaya.</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Fight Club</t>
+          <t>Câu Lạc Bộ Đấu Võ</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Tất cả That Glitters</t>
+          <t>Vẻ Hào Nhoáng Muôn Màu</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Thử Calcite Đi!</t>
+          <t>Thử Calcite đi!</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Gió Trong Gương</t>
+          <t>Gió trong Gương</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Hope Lies Beyond Despair</t>
+          <t>Hy Vọng Nằm Ngoài Bóng Tối Tuyệt Vọng</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Judgment Ngày</t>
+          <t>Ngày Phán Xét</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Bạn Shall Not Pass</t>
+          <t>Ngươi sẽ không qua được đâu!</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Mũi Tên Của Sự Phạm Tội</t>
+          <t>Mũi tên của Sự Vi Phạm</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Recitativo Di Lode</t>
+          <t>Khúc Ngâm Vinh Danh</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Cold-Hardy</t>
+          <t>Lạnh?</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Lightning Conductor</t>
+          <t>Dẫn Điện</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Khai Thác Sức Gió</t>
+          <t>Thuần Hóa Gió</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Tan Biến Cùng Cơn Gió</t>
+          <t>Tan Theo Gió</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Jellyfish Locker</t>
+          <t>Tủ Đựng Đồ Sứa</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Miss Golden Week</t>
+          <t>Chị Golden Week</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Hiện Tại Ta Mạnh Hơn Ngươi</t>
+          <t>Ta mạnh hơn ngươi... hiện tại là vậy.</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>I Barely Tried</t>
+          <t>Ta còn chưa thử sức hết mình.</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Có Một Bậc Thầy Khác Sao?</t>
+          <t>Có một Master khác sao?</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Friend, Times Have Changed</t>
+          <t>Bạn ơi, thời thế đã đổi thay rồi...</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Sức Mạnh Cấp Độ Năm</t>
+          <t>Cấp Độ Sức Mạnh 5</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Magus Killer</t>
+          <t>Sát Thủ Magus</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Plushie - Mega Evolution</t>
+          <t>Bông Gòn - Tiến Hóa Siêu Cấp</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Torn Plushie, Lost Song</t>
+          <t>Gấu Bông Rách, Bản Nhạc Thất Lạc</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Sapphire Star</t>
+          <t>Ngôi Sao Lam</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Salvation Lies Within</t>
+          <t>Ơn Cứu Rỗi Nằm Trong Ta</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Bị Cuộc Đời Ghét Bỏ</t>
+          <t>Bị Cuộc Đời Căm Ghét</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Enhanced Dragon Slave</t>
+          <t>Bão Rồng Cường Hóa</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Dragon Slayer</t>
+          <t>Diệt Rồng</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Dragon Slayer Magic</t>
+          <t>Phép Thuật Diệt Rồng</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Trở Thành Cơn Gió</t>
+          <t>Trở thành Gió</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Pilum Tactics</t>
+          <t>Chiến Thuật Pilum</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Vở Diễn Không Có Hồi Kết</t>
+          <t>Vở Kịch Không Có Hồi Kết</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Thalassophobia</t>
+          <t>Hội chứng sợ biển sâu</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Người Điều Khiển Số Mệnh</t>
+          <t>Người Chấp Pháp Của Định Mệnh</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Veni, Vidi</t>
+          <t>Ta đến, ta thấy</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Ánh Bạc Lặng Lẽ Trút Xuống</t>
+          <t>Ánh Bạc Lặng Thầm Trút Xuống</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Hunt Bạn Down</t>
+          <t>Tao sẽ săn mày đến cùng</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>False Compassion</t>
+          <t>Lòng thương giả tạo</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>One Hundred Shots</t>
+          <t>Trăm Phát Bắn</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Blind Watcher</t>
+          <t>Giám Thị Mù</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Từ Vực Sâu Đến Vực Sâu</t>
+          <t>Từ Vực Sâu, về Vực Sâu</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Thảm Họa Luôn Theo Sau Bước Chân</t>
+          <t>Thảm họa luôn rình rập ngay phía sau</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Deserted Trail</t>
+          <t>Lối Mòn Bỏ Hoang</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>When Aix Cries</t>
+          <t>Khi Aix Khóc</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>When Aix Cries</t>
+          <t>Khi Aix Khóc</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Beringal, We're Goin Down</t>
+          <t>Beringal, Chúng Ta Đang Lao Xuống</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Cưỡi Lửa Địa Ngục</t>
+          <t>Lướt trên Lửa Địa Ngục</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Crown Fallen</t>
+          <t>Vương Miện Đổ Vỡ</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Chỉ Có Chuông Vẫn Ngân</t>
+          <t>Chỉ Chuông Ngân Lên</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Dancing Flash</t>
+          <t>Tia chớp nhảy múa</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Dậy Đi, Dậy Đi!</t>
+          <t>Dậy nào, dậy nào!</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Không Liz, Nhưng Strange Birds</t>
+          <t>Không có Liz, chỉ thấy mấy con chim lạ</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Thống Lĩnh Rừng Xanh</t>
+          <t>Thống Trị Rừng Xanh</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Xuyên Màn Sương Bằng Ánh Sáng</t>
+          <t>Xuyên Sương Bằng Ánh Sáng</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Night Voyager</t>
+          <t>Hành Trình Đêm</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Chiếm Lấy Ngai Vàng</t>
+          <t>Lấy Vương Miện</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Fatal Strike</t>
+          <t>Đòn Tấn Công Tử Thần</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Fading Tempest</t>
+          <t>Bão Tố Nhạt Nhoà</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Silent Burst</t>
+          <t>Vụ Nổ Im Lặng</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>A Lethal Weapon</t>
+          <t>Một Vũ Khí Sát Thủ</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Returning Echo</t>
+          <t>Tiếng Vọng Trở Về</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hạt Giống Phù Thủy</t>
+          <t>Hạt giống Phù Thủy</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>The Darkest Hour</t>
+          <t>Giờ Khắc Tăm Tối Nhất</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Vũ Khí Bí Mật Của Một Tăng Sĩ</t>
+          <t>Vũ Khí Bí Truyền của Một Tăng Lữ</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Tia Chớp Đầu Tiên</t>
+          <t>Tia Sét Đầu Tiên</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Sân Khấu Của Nữ Anh Hùng</t>
+          <t>Sân Khấu Nữ Anh Hùng</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Blooming Snow</t>
+          <t>Tuyết Hoa Nở Rộ</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Phòng Thủ Là Tấn Công Tốt Nhất</t>
+          <t>Phòng Ngự Là Tấn Công Tốt Nhất</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Triệu hồi Gió Ngàn</t>
+          <t>Triệu Hồi Gió Ngàn</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Zapstring's Hiss</t>
+          <t>Tiếng Rít Của Dây Sét</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Lush Garden's Keeper</t>
+          <t>Người Trông Nom Vườn Xanh Mướt</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Brave Wooly</t>
+          <t>Chú Cừu Dũng Cảm</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Câu trả lời là 42</t>
+          <t>Câu Trả Lời Là 42</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Lion - Kẻ Cai Trị</t>
+          <t>Sư Tử Chúa Tể</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Dragon's Breath</t>
+          <t>Hơi Thở Rồng</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>A Mild Combat</t>
+          <t>Một Trận Chiến Nhẹ Nhàng</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Theo dấu Thanh Long</t>
+          <t>Theo Long Thanh</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Viên Đạn Bạc</t>
+          <t>Đạn Bạc</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>By Tất cả Means</t>
+          <t>Bằng mọi giá</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Silent Mode</t>
+          <t>Chế Độ Vô Thanh</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Dimming Shadows</t>
+          <t>Bóng Tối Mờ Dần</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Trong như Gương</t>
+          <t>Trong như gương.</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Jué Is With Me</t>
+          <t>Jué Đang Ở Bên Ta</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Món Quà Lửa Đỏ</t>
+          <t>Món Quà Của Lửa</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Sắc Đẹp và Lưỡi Kiếm</t>
+          <t>Mỹ nhân và Lưỡi Kiếm</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Cơn Mưa Hoa</t>
+          <t>Bão Hoa</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Everlasting Blossoms</t>
+          <t>Hoa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Birds' Ballad</t>
+          <t>Khúc Ballad Của Loài Chim</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Warm Yet Solitary</t>
+          <t>Ấm Áp Nhưng Cô Đơn</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Folded Petals</t>
+          <t>Cánh Hoa Gấp</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Encore's Wonderous Adventures</t>
+          <t>Những Chuyến Phiêu Lưu Kỳ Thú Của Encore</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Nhịp Đập Sinh Mệnh</t>
+          <t>Nhịp Đập Sự Sống</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Good Omen</t>
+          <t>Điềm Lành</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Hạ Gục Bằng Lôi Hoàng Quyền!</t>
+          <t>Đấm Nát Bằng Lôi Hoàng Quyền!</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Biến Hóa Của Thanh Long Mưa</t>
+          <t>Biến thân: Vũ Long Mưa</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Veiled Gunfire</t>
+          <t>Bắn Phá Bên Dưới Bức Màn</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Shadow Boxing</t>
+          <t>Đấm Bóng</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Eternal Flame</t>
+          <t>Ngọn Lửa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Bàn Tay Của Thượng Đế!</t>
+          <t>Bàn tay của Chúa!</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>The Silent Deity</t>
+          <t>Vị Thần Câm Lặng</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Loong Lineage</t>
+          <t>Dòng Dõi Rồng</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Ngươi Là Kẻ Thách Đấu!</t>
+          <t>Cậu chính là Người Thách Đấu!</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>20 Constructss</t>
+          <t>20 Construct</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Kill It With Heat</t>
+          <t>Tiêu Diệt Bằng Sức Nóng</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Tất Cả Đều Là Protein?</t>
+          <t>Toàn Là Protein À?</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Kẻ Khuất Phục Hổ</t>
+          <t>Kẻ Khuất Phục Hổ Lang</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Nếu Ta Được Thấu Tri Thức</t>
+          <t>Nếu Ta Được Thấu Tri Kiến...</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>A Sight To Remember</t>
+          <t>Cảnh Tượng Đáng Nhớ</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Bươm Bướm Không Bay Được Trong Đêm</t>
+          <t>Bướm Không Bay Được Trong Đêm</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Jackpot</t>
+          <t>Trúng lớn rồi!</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Hạt Giống Phù Thủy</t>
+          <t>Hạt giống Phù Thủy</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Lumi's Delivery Service</t>
+          <t>Dịch Vụ Giao Hàng Lumi</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Sức Mạnh Thật Sự!</t>
+          <t>Sức Mạnh Chân Chính!</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>The Grand Master</t>
+          <t>Đại Sư Phụ</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Master Damage I</t>
+          <t>Sư phụ Sát Thương I</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Master Damage II</t>
+          <t>Sư phụ Sát Thương II</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Master Damage III</t>
+          <t>Sư phụ Sát Thương III</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Master Damage IV</t>
+          <t>Sư phụ Sát Thương IV</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>"Ta chọn hình dạng của Tacet Discord!"</t>
+          <t>"Ta chọn hình thái của Tacet Discord!"</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Turtle Breathing</t>
+          <t>Hơi Thở Rùa</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Tiến Lên Và Chiến Đấu!</t>
+          <t>Tiến lên chiến đấu!</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>The Unbearable Strike Of Being</t>
+          <t>Cú Đòn Không Thể Chịu Đựng</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>One Punch, Problem Solved</t>
+          <t>Một Cú Đấm, Vấn Đề Giải Quyết</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Chỉ Cần Búng Ngón Tay</t>
+          <t>Chỉ trong nháy mắt</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Godlike Power I</t>
+          <t>Sức Mạnh Thần Thánh I</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Godlike Power II</t>
+          <t>Sức Mạnh Thần Thánh II</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Godlike Power III</t>
+          <t>Sức Mạnh Thần Thánh III</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Godlike Power IV</t>
+          <t>Sức Mạnh Thần Thánh IV</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Godlike Power V</t>
+          <t>Sức Mạnh Thần Thánh V</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Source Code</t>
+          <t>Mã Nguồn</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Lỗi: không tìm thấy đối tượng</t>
+          <t>Lỗi: Không tìm thấy đối tượng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Tất cả Coming Together</t>
+          <t>Tất Cả Hợp Nhất</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Khó Work Pays Off</t>
+          <t>Nỗ Lực Sẽ Được Đền Đáp</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Forged In Fire</t>
+          <t>Rèn Trong Lửa Đỏ</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Curtain Call</t>
+          <t>Điểm cuối màn diễn</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Escape Plan</t>
+          <t>Kế Hoạch Thoát Hiểm</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Daydreamer</t>
+          <t>Kẻ Mộng Mơ</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Hai Mươi Đêm Mộng Mị</t>
+          <t>Hai Mươi Đêm Mộng Ảo</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Broken Windows Theory</t>
+          <t>Thuyết Cửa Sổ Vỡ</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Lights Off</t>
+          <t>Tắt Đèn</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>White Devil</t>
+          <t>Ác Quỷ Trắng</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Lời Thề, Sự Chuyển Biến và Ảo Thuật</t>
+          <t>Lời Thề, Sự Chuyển Mình và Phép Màu</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Lost Stars</t>
+          <t>Những Vì Sao Lạc Lối</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Sẵn Sàng Làm Việc</t>
+          <t>Sẵn sàng làm việc thôi</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Dynamax Plushie</t>
+          <t>Gấu bông Dynamax</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Danh Xưng Nặng Trĩu</t>
+          <t>Danh Hiệu Nặng Trịch</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Blade Waltz</t>
+          <t>Điệu Vals Kiếm</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Aquatic Grace</t>
+          <t>Ân Sủng Thủy Tinh</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>One Shot, Three Echoes</t>
+          <t>Một Phát, Ba Echo</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Hơi Sang Trái Một Chút</t>
+          <t>Hơi Sang Trái</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Hơi Sang Phải Một Chút</t>
+          <t>Hơi Sang Phải</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Bullseye</t>
+          <t>Trúng đích!</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Loại Sản Xuất Hàng Loạt L</t>
+          <t>Mẫu L Sản Xuất Hàng Loạt</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>When Clouds Settle</t>
+          <t>Khi Mây Tan</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>The Rampage</t>
+          <t>Cơn Thịnh Nộ</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Endless Rondo</t>
+          <t>Vô Tận Luân Khúc</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Handy Pistols I</t>
+          <t>Súng Ngắn Tiện Dụng I</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Handy Pistols II</t>
+          <t>Súng Ngắn Tiện Dụng II</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Nơi Mới Thay Thế Cũ</t>
+          <t>Nơi Chốn Xưa Cũ Mới</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>The Dark Knight Rises</t>
+          <t>Hắc Kỵ Sĩ Trỗi Dậy</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Goodnight, Snip Snaps</t>
+          <t>Chúc ngủ ngon, lũ Snip Snaps nhé.</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Tắt Đèn...</t>
+          <t>Tắt Đèn... Hết.</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Tiếng Loảng Xoảng</t>
+          <t>Ầm ĩ &amp; Vang Dội</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Đánh Hơi Mùi Whiff</t>
+          <t>Đánh hơi mùi nào</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>A Silent Tick</t>
+          <t>Tiếng Kim Đồng Hồ Vô Thanh</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>A Deadly Weight</t>
+          <t>Gánh Nặng Chết Người</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Unexpected Disaster</t>
+          <t>Thảm họa bất ngờ</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>DANGEROUS CREATURE</t>
+          <t>SINH VẬT NGUY HIỂM</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Thức Dậy Nào</t>
+          <t>Dậy Đi Nào</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Chilling Frost</t>
+          <t>Sương Giá Lạnh Lùng</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Scorching Sun</t>
+          <t>Mặt Trời Nóng Rực</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Noisy Wind</t>
+          <t>Tiếng Gió Gào Thét</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Over-Photosynthesis</t>
+          <t>Quang Hợp Quá Mức</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Nhắm Mắt Khi Trời Tối</t>
+          <t>Hãy Nhắm Mắt Khi Bóng Tối Buông Xuống</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Chain Reaction</t>
+          <t>Phản Ứng Dây Xích</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Đừng Lặng Lẽ Chìm Vào Đêm Tốt Lành</t>
+          <t>Đừng Lặng Lẽ Tan Vào Đêm Tốt Lành Đó</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Ghost of Dark Forest: Hunter</t>
+          <t>Thợ Săn Rừng U Minh: Ma</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Ghost of Dark Forest: Stroller</t>
+          <t>Kẻ Lang Thang Rừng U Minh: Ma</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Ghost of Dark Forest: Lurker</t>
+          <t>Kẻ Rình Rập Rừng U Minh: Ma</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Ghost of Dark Forest: Observer</t>
+          <t>Kẻ Quan Sát Rừng U Minh: Ma</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Sấm Sét Trong Biển Lửa</t>
+          <t>Sấm Gầm trên Biển Lửa</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Gặp Gỡ Đức Vua</t>
+          <t>Gặp gỡ Đức Vua</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Moment Once More</t>
+          <t>Khoảnh khắc một lần nữa</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Thunder Silencer</t>
+          <t>Lôi Âm Trầm</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Khúc Bi Ca Tàn</t>
+          <t>Dies the Elegy</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Không Thấy Đức Vua Đâu</t>
+          <t>Không thấy Vua đâu cả</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Nhanh và Gian Nan</t>
+          <t>Nhanh &amp; Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Invincible</t>
+          <t>Bất khả chiến bại</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Three Sunsets</t>
+          <t>Ba Hoàng Hôn</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Tới Những Kẻ Vinh Quang</t>
+          <t>Tới Những Vị Vinh Quang</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>The Crownless King</t>
+          <t>Vua Không Vương Miện</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Thất Bại Không Có Trong Từ Điển Của Ta</t>
+          <t>Thất bại không có trong từ điển của ta</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Rider's Offering</t>
+          <t>Lễ Vật Kỵ Sĩ</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Đánh Bại Chúng, Rover!</t>
+          <t>Đánh gục chúng đi, Vận Mệnh Giả!</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Star Platinum</t>
+          <t>Bạch Kim Sao</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Five Seconds Isn't Enough</t>
+          <t>Năm Giây Vẫn Chưa Đủ</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Trong Chiến Đấu Gần, Lợi Thế Là Của Ta!</t>
+          <t>Trong Chiến Đấu Cận Chiến, Lợi Thế Là Của Ta!</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Nó Đã Cứu Nhiều Mạng Hơn Bạn Tưởng!</t>
+          <t>Nó đã cứu sống nhiều mạng hơn mày tưởng tượng được đấy!</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Deep Sea Voyage: Setting Sail</t>
+          <t>Hành Trình Vực Sâu: Khởi Hành</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Deep Sea Voyage: Into Depths</t>
+          <t>Hành Trình Vực Sâu: Lặn Xuống Đáy</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Deep Sea Voyage: Pioneering</t>
+          <t>Hành Trình Vực Sâu: Tiên Phong Khai Phá</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Selective Attendance Protocol</t>
+          <t>Giao Thức Tham Gia Có Điều Kiện</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Final Plan Approved</t>
+          <t>Kế Hoạch Cuối Cùng Đã Được Phê Duyệt</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Trong Những Bóng Tối Dâng Lên</t>
+          <t>Trong Những Bóng Tối Trỗi Dậy</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Từ "Dear" Đến "Deer"</t>
+          <t>Từ Dear đến Deer</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Không Longer Deerailed</t>
+          <t>Không còn trật bánh nữa</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Không Hoofing Around</t>
+          <t>Đừng có đùa giỡn</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Reaver Reaper</t>
+          <t>Kẻ Gặt Hái Tàn Phá</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Invisible Foe</t>
+          <t>Kẻ Thù Vô Hình</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Shell Runner</t>
+          <t>Kẻ Đuổi Bóng</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Đi Theo Con Đường Coleoid...</t>
+          <t>Đi theo lối Coleoid...</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>The Hive's Greenhorn</t>
+          <t>Tân binh của Tổ Ong</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Leave Không Stone Un-Buzzed</t>
+          <t>Rời khỏi Không Đá Nào Lặng Im</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Geospider Man</t>
+          <t>Người Nhện Địa Chấn</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Tóc Đuôi Ngựa Trên Chiến Trường Săn Bắn</t>
+          <t>Bím tóc trên Bãi Săn</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Bị Điện Giật...</t>
+          <t>Đã phóng điện...</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>The Great Seal</t>
+          <t>Ấn Đại Phong Ấn</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Your Golden Time</t>
+          <t>Thời Khắc Vàng Son Của Cậu</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Predestination</t>
+          <t>Định Mệnh</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>What Planet Is This</t>
+          <t>Hành Tinh Này Là Gì Thế?</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>High-Rise Invasion</t>
+          <t>Xâm Nhập Tòa Cao Ốc</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Không Có Chim Bay Lượn</t>
+          <t>Chẳng còn cánh chim nào bay</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Colder Than Ice</t>
+          <t>Sự lạnh lẽo và cái chết vương đầy những ngóc ngách tối tăm này.</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>The Shadow Thief</t>
+          <t>Kẻ Trộm Bóng Tối</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Doppelganger</t>
+          <t>Bản Sao Ác Mộng</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Trở Về Vũ Trụ</t>
+          <t>Trở về với vũ trụ</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Sấm Chớp và Bão Tố</t>
+          <t>Sấm Sét và Bão Tố</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Ancient Zoan</t>
+          <t>Zoan cổ đại</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>The Primeval Call</t>
+          <t>Lời Kêu Gọi Nguyên Sơ</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Black Swan</t>
+          <t>Thiên Nga Đen</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Shadows Die Once</t>
+          <t>Bóng Tối Chỉ Chết Một Lần</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Tất cả Battles Won I</t>
+          <t>Chiến Thắng Toàn Bộ Trận I</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Em Thậm Chí Còn Không Muốn Gọi Anh Là Anh Trai Cơ!</t>
+          <t>Em Không Thèm Gọi Anh Là Anh Trai Hả!</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Beginner Pet Raising</t>
+          <t>Nuôi Thú Cưng Cơ Bản</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Khi Những Vì Sao Chói Lọi I</t>
+          <t>Khi Những Vì Sao Chiếu Sáng I</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Khi Những Vì Sao Chói Lọi II</t>
+          <t>Khi Những Vì Sao Chiếu Sáng II</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Khi Những Vì Sao Chói Lọi III</t>
+          <t>Khi Sao Sáng Lên III</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Your Friendly Neighborhood Rover I</t>
+          <t>Rover Hàng Xóm Tốt Bụng I</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Your Friendly Neighborhood Rover II</t>
+          <t>Rover Hàng Xóm Tốt Bụng II</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Your Friendly Neighborhood Rover III</t>
+          <t>Rover Hàng Xóm Tốt Bụng III</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>First Try</t>
+          <t>Lần Thử Đầu Tiên</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Tất cả Battles Won II</t>
+          <t>Chiến Thắng Toàn Bộ Trận II</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Tất cả Battles Won III</t>
+          <t>Chiến Thắng Toàn Bộ Trận III</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>"Ta Mỏng Manh Đã Chết Rồi"</t>
+          <t>"Ta Đã Chết Yểu"</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Unfamiliar Ceiling</t>
+          <t>Trần nhà lạ lẫm</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Hạng Này Đến Hạng Khác</t>
+          <t>Cấp Cao Hơn Cấp</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
